--- a/data/brasil/clubes/uniformes_2026.xlsx
+++ b/data/brasil/clubes/uniformes_2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG278"/>
+  <dimension ref="A1:AG284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5322,123 +5322,38 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Penedense</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Penedense</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>#D71920</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>https://www.footballkitarchive.com/sc-penedense-kits-2026-t66920/</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>#D71920</t>
+          <t>ADESG</t>
         </is>
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Porto Velho</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>#072061</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>#C3131A</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>#FEFEFE</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>https://www.footballkitarchive.com/porto-velho-2026-kits/</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>#C3131A</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>#072061</t>
+          <t>Galvez</t>
         </is>
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Humaitá</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Humaitá</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>#E20917</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>#029E51</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>#FDFDFD</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>https://www.footballkitarchive.com/sc-humaita-2026-kits/</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>#029E51</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>#E20917</t>
+          <t>Rio Branco-AC</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5365,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ADESG</t>
+          <t>Santa Cruz-AC</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5377,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>São Francisco-AC</t>
         </is>
       </c>
     </row>
@@ -5474,19 +5389,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rio Branco-AC</t>
+          <t>Vasco-AC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>São Francisco-AC</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5413,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Coruripe</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5425,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Coruripe</t>
+          <t>Cruzeiro de Arapiraca</t>
         </is>
       </c>
     </row>
@@ -5522,19 +5437,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cruzeiro de Arapiraca</t>
+          <t>Murici SC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Murici SC</t>
+          <t>Itacoatiara</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5461,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Itacoatiara</t>
+          <t>Nacional</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5473,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Parintins</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5485,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Parintins</t>
+          <t>Princesa do Solimões</t>
         </is>
       </c>
     </row>
@@ -5582,19 +5497,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Princesa do Solimões</t>
+          <t>São Raimundo-AM</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>São Raimundo-AM</t>
+          <t>Cristal</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5521,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cristal</t>
+          <t>Independente</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5533,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Independente</t>
+          <t>Macapá</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5545,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Macapá</t>
+          <t>Oratório</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5557,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Oratório</t>
+          <t>Santos-AP</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5876,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ABECAT</t>
+          <t>Vitória-ES</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5893,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Anapolina</t>
+          <t>ABECAT</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5905,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>Anapolina</t>
         </is>
       </c>
     </row>
@@ -6002,7 +5917,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Centro Oeste</t>
+          <t>CRAC</t>
         </is>
       </c>
     </row>
@@ -6014,7 +5929,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Inhumas</t>
+          <t>Centro Oeste</t>
         </is>
       </c>
     </row>
@@ -6026,19 +5941,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jataiense</t>
+          <t>Inhumas</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IAPE</t>
+          <t>Jataiense</t>
         </is>
       </c>
     </row>
@@ -6050,7 +5965,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ITZ Sport</t>
+          <t>IAPE</t>
         </is>
       </c>
     </row>
@@ -6062,7 +5977,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Luminense</t>
+          <t>ITZ Sport</t>
         </is>
       </c>
     </row>
@@ -6074,7 +5989,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Moto Club</t>
+          <t>Luminense</t>
         </is>
       </c>
     </row>
@@ -6086,19 +6001,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tuntum</t>
+          <t>Moto Club</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Betim</t>
+          <t>Tuntum</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6025,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Democrata GV</t>
+          <t>Betim</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6037,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Democrata GV</t>
         </is>
       </c>
     </row>
@@ -6134,19 +6049,19 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>North</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bataguassu</t>
+          <t>URT</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6073,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>Bataguassu</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6085,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Corumbaense</t>
+          <t>CRA</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6097,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Corumbaense</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6109,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dourados</t>
+          <t>Costa Rica</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6121,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FC Pantanal</t>
+          <t>Dourados</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6133,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ivinhema</t>
+          <t>FC Pantanal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6145,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Naviraiense</t>
+          <t>Ivinhema</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6157,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pantanal</t>
+          <t>Naviraiense</t>
         </is>
       </c>
     </row>
@@ -6254,19 +6169,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Águia Negra</t>
+          <t>Pantanal</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chapada</t>
+          <t>Águia Negra</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6193,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nova Mutum</t>
+          <t>Chapada</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6205,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Operário VG</t>
+          <t>Nova Mutum</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6217,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Operário VG</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6229,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sport Sinop</t>
+          <t>Primavera</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6241,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>União Rondonópolis</t>
+          <t>Sport Sinop</t>
         </is>
       </c>
     </row>
@@ -6338,19 +6253,19 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Várzea Grande</t>
+          <t>União Rondonópolis</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Amazônia</t>
+          <t>Várzea Grande</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6277,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cametá</t>
+          <t>Amazônia</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6289,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capitão Poço</t>
+          <t>Bragantino-PA</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6301,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Castanhal</t>
+          <t>Cametá</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6313,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Capitão Poço</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6325,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>São Francisco-PA</t>
+          <t>Castanhal</t>
         </is>
       </c>
     </row>
@@ -6422,31 +6337,31 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>São Raimundo-PA</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Atlético de Cajazeiras</t>
+          <t>São Francisco-PA</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Campinense</t>
+          <t>São Raimundo-PA</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6373,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Confiança de Sapé</t>
+          <t>Atlético de Cajazeiras</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6385,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Esporte de Patos</t>
+          <t>Campinense</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6397,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nacional de Patos</t>
+          <t>Confiança de Sapé</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6409,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Pombal</t>
+          <t>Esporte de Patos</t>
         </is>
       </c>
     </row>
@@ -6506,31 +6421,31 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Serra Branca</t>
+          <t>Nacional de Patos</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Decisão</t>
+          <t>Pombal</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Decisão Goiana</t>
+          <t>Serra Branca</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6457,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Jaguar</t>
+          <t>Decisão</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6469,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Maguary</t>
+          <t>Decisão Goiana</t>
         </is>
       </c>
     </row>
@@ -6566,31 +6481,31 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vitória das Tabocas</t>
+          <t>Jaguar</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Atlético Piauiense</t>
+          <t>Maguary</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Corisabbá</t>
+          <t>Vitória das Tabocas</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6517,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Oeirense</t>
+          <t>Atlético Piauiense</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6529,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Corisabbá</t>
         </is>
       </c>
     </row>
@@ -6626,43 +6541,43 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Teresina</t>
+          <t>Fluminense-PI</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Andraus</t>
+          <t>Oeirense</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Cascavel</t>
+          <t>Piauí</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Foz do Iguaçu</t>
+          <t>Teresina</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6589,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Galo Maringá</t>
+          <t>Andraus</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6601,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PSTC/São Joseense</t>
+          <t>Cascavel</t>
         </is>
       </c>
     </row>
@@ -6698,103 +6613,103 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>São Joseense</t>
+          <t>Foz do Iguaçu</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>América-RJ</t>
+          <t>Galo Maringá</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Bangu</t>
+          <t>PSTC/São Joseense</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Madureira</t>
+          <t>São Joseense</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Globo</t>
+          <t>América-RJ</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Laguna</t>
+          <t>Bangu</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Parnamirim/ABC-D</t>
+          <t>Madureira</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Potiguar de Mossoró</t>
+          <t>Portuguesa-RJ</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Potyguar Seridoense</t>
+          <t>Sampaio Corrêa-RJ</t>
         </is>
       </c>
     </row>
@@ -6806,67 +6721,67 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>QFC</t>
+          <t>Globo</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Barcelona-RO</t>
+          <t>Laguna</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Genus</t>
+          <t>Parnamirim/ABC-D</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Guaporé</t>
+          <t>Potiguar de Mossoró</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Potyguar Seridoense</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Rondoniense</t>
+          <t>QFC</t>
         </is>
       </c>
     </row>
@@ -6878,67 +6793,67 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>União Cacoalense</t>
+          <t>Barcelona-RO</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Atlético Roraima</t>
+          <t>Genus</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Baré</t>
+          <t>Guaporé</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Monte Roraima</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Progresso</t>
+          <t>Rondoniense</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Rio Negro-RR</t>
+          <t>União Cacoalense</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6865,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>River-RR</t>
+          <t>Atlético Roraima</t>
         </is>
       </c>
     </row>
@@ -6962,317 +6877,389 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>São Raimundo-RR</t>
+          <t>Baré</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Avenida</t>
+          <t>Monte Roraima</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Internacional de Santa Maria</t>
+          <t>Náutico-RR</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Monsoon</t>
+          <t>Progresso</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Rio Negro-RR</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Blumenau</t>
+          <t>River-RR</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Camboriú</t>
+          <t>São Raimundo-RR</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Carlos Renaux</t>
+          <t>Avenida</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Concórdia</t>
+          <t>Internacional de Santa Maria</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Monsoon</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>América de Propriá</t>
+          <t>Novo Hamburgo</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Atlético Gloriense</t>
+          <t>Blumenau</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Desportiva Aracaju</t>
+          <t>Camboriú</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Dorense</t>
+          <t>Carlos Renaux</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Falcon</t>
+          <t>Concórdia</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Guarany de Porto da Folha</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Capivariano</t>
+          <t>América de Propriá</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Noroeste</t>
+          <t>Atlético Gloriense</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Primavera-SP</t>
+          <t>Desportiva Aracaju</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Velo Clube</t>
+          <t>Dorense</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>XV de Piracicaba</t>
+          <t>Falcon</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Araguaína</t>
+          <t>Guarany de Porto da Folha</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Bela Vista</t>
+          <t>Capivariano</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Capital-TO</t>
+          <t>Noroeste</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Guaraí</t>
+          <t>Primavera-SP</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Gurupi</t>
+          <t>Velo Clube</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>XV de Piracicaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Araguaína</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Bela Vista</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Capital-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Guaraí</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Gurupi</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
